--- a/Australia/data_raw/3101059.xlsx
+++ b/Australia/data_raw/3101059.xlsx
@@ -61912,292 +61912,292 @@
         <v>45809</v>
       </c>
       <c r="B65" s="8">
-        <v>153974</v>
+        <v>153971</v>
       </c>
       <c r="C65" s="8">
-        <v>150216</v>
+        <v>150180</v>
       </c>
       <c r="D65" s="8">
-        <v>152822</v>
+        <v>152801</v>
       </c>
       <c r="E65" s="8">
-        <v>162808</v>
+        <v>162794</v>
       </c>
       <c r="F65" s="8">
-        <v>159119</v>
+        <v>159109</v>
       </c>
       <c r="G65" s="8">
-        <v>158375</v>
+        <v>158369</v>
       </c>
       <c r="H65" s="8">
-        <v>162859</v>
+        <v>162845</v>
       </c>
       <c r="I65" s="8">
-        <v>163901</v>
+        <v>163903</v>
       </c>
       <c r="J65" s="8">
-        <v>167280</v>
+        <v>167277</v>
       </c>
       <c r="K65" s="8">
-        <v>172027</v>
+        <v>172031</v>
       </c>
       <c r="L65" s="8">
-        <v>171290</v>
+        <v>171314</v>
       </c>
       <c r="M65" s="8">
         <v>172596</v>
       </c>
       <c r="N65" s="8">
-        <v>174656</v>
+        <v>174663</v>
       </c>
       <c r="O65" s="8">
-        <v>173954</v>
+        <v>173959</v>
       </c>
       <c r="P65" s="8">
-        <v>172689</v>
+        <v>172693</v>
       </c>
       <c r="Q65" s="8">
-        <v>174298</v>
+        <v>174305</v>
       </c>
       <c r="R65" s="8">
-        <v>173451</v>
+        <v>173418</v>
       </c>
       <c r="S65" s="8">
-        <v>173684</v>
+        <v>173646</v>
       </c>
       <c r="T65" s="8">
-        <v>176661</v>
+        <v>176677</v>
       </c>
       <c r="U65" s="8">
-        <v>178955</v>
+        <v>178842</v>
       </c>
       <c r="V65" s="8">
-        <v>181661</v>
+        <v>181679</v>
       </c>
       <c r="W65" s="8">
-        <v>183017</v>
+        <v>183010</v>
       </c>
       <c r="X65" s="8">
-        <v>184702</v>
+        <v>184666</v>
       </c>
       <c r="Y65" s="8">
-        <v>191590</v>
+        <v>191482</v>
       </c>
       <c r="Z65" s="8">
-        <v>202445</v>
+        <v>202239</v>
       </c>
       <c r="AA65" s="8">
-        <v>205439</v>
+        <v>205325</v>
       </c>
       <c r="AB65" s="8">
-        <v>203567</v>
+        <v>203459</v>
       </c>
       <c r="AC65" s="8">
-        <v>205386</v>
+        <v>205360</v>
       </c>
       <c r="AD65" s="8">
-        <v>206853</v>
+        <v>206850</v>
       </c>
       <c r="AE65" s="8">
-        <v>207872</v>
+        <v>207871</v>
       </c>
       <c r="AF65" s="8">
-        <v>210038</v>
+        <v>210055</v>
       </c>
       <c r="AG65" s="8">
-        <v>206335</v>
+        <v>206219</v>
       </c>
       <c r="AH65" s="8">
-        <v>204273</v>
+        <v>204181</v>
       </c>
       <c r="AI65" s="8">
-        <v>202323</v>
+        <v>202274</v>
       </c>
       <c r="AJ65" s="8">
-        <v>204977</v>
+        <v>204973</v>
       </c>
       <c r="AK65" s="8">
-        <v>204918</v>
+        <v>204890</v>
       </c>
       <c r="AL65" s="8">
-        <v>201309</v>
+        <v>201290</v>
       </c>
       <c r="AM65" s="8">
-        <v>198157</v>
+        <v>198123</v>
       </c>
       <c r="AN65" s="8">
-        <v>198015</v>
+        <v>197998</v>
       </c>
       <c r="AO65" s="8">
-        <v>198657</v>
+        <v>198629</v>
       </c>
       <c r="AP65" s="8">
-        <v>196485</v>
+        <v>196456</v>
       </c>
       <c r="AQ65" s="8">
-        <v>194294</v>
+        <v>194266</v>
       </c>
       <c r="AR65" s="8">
-        <v>193265</v>
+        <v>193257</v>
       </c>
       <c r="AS65" s="8">
-        <v>186414</v>
+        <v>186390</v>
       </c>
       <c r="AT65" s="8">
-        <v>179678</v>
+        <v>179664</v>
       </c>
       <c r="AU65" s="8">
-        <v>169882</v>
+        <v>169890</v>
       </c>
       <c r="AV65" s="8">
-        <v>164952</v>
+        <v>164941</v>
       </c>
       <c r="AW65" s="8">
-        <v>159825</v>
+        <v>159824</v>
       </c>
       <c r="AX65" s="8">
-        <v>158601</v>
+        <v>158613</v>
       </c>
       <c r="AY65" s="8">
-        <v>159801</v>
+        <v>159794</v>
       </c>
       <c r="AZ65" s="8">
-        <v>160630</v>
+        <v>160631</v>
       </c>
       <c r="BA65" s="8">
-        <v>162562</v>
+        <v>162546</v>
       </c>
       <c r="BB65" s="8">
-        <v>165647</v>
+        <v>165642</v>
       </c>
       <c r="BC65" s="8">
-        <v>170432</v>
+        <v>170448</v>
       </c>
       <c r="BD65" s="8">
-        <v>171158</v>
+        <v>171136</v>
       </c>
       <c r="BE65" s="8">
-        <v>160094</v>
+        <v>160095</v>
       </c>
       <c r="BF65" s="8">
-        <v>157171</v>
+        <v>157159</v>
       </c>
       <c r="BG65" s="8">
-        <v>150676</v>
+        <v>150662</v>
       </c>
       <c r="BH65" s="8">
-        <v>147255</v>
+        <v>147256</v>
       </c>
       <c r="BI65" s="8">
-        <v>146495</v>
+        <v>146470</v>
       </c>
       <c r="BJ65" s="8">
-        <v>147434</v>
+        <v>147416</v>
       </c>
       <c r="BK65" s="8">
-        <v>151046</v>
+        <v>151031</v>
       </c>
       <c r="BL65" s="8">
-        <v>152171</v>
+        <v>152157</v>
       </c>
       <c r="BM65" s="8">
-        <v>150268</v>
+        <v>150227</v>
       </c>
       <c r="BN65" s="8">
-        <v>147481</v>
+        <v>147425</v>
       </c>
       <c r="BO65" s="8">
-        <v>140886</v>
+        <v>140810</v>
       </c>
       <c r="BP65" s="8">
-        <v>137536</v>
+        <v>137521</v>
       </c>
       <c r="BQ65" s="8">
-        <v>133166</v>
+        <v>133162</v>
       </c>
       <c r="BR65" s="8">
-        <v>128891</v>
+        <v>128871</v>
       </c>
       <c r="BS65" s="8">
-        <v>125917</v>
+        <v>125892</v>
       </c>
       <c r="BT65" s="8">
-        <v>120306</v>
+        <v>120291</v>
       </c>
       <c r="BU65" s="8">
-        <v>115798</v>
+        <v>115782</v>
       </c>
       <c r="BV65" s="8">
-        <v>113976</v>
+        <v>113966</v>
       </c>
       <c r="BW65" s="8">
-        <v>109661</v>
+        <v>109641</v>
       </c>
       <c r="BX65" s="8">
-        <v>107328</v>
+        <v>107354</v>
       </c>
       <c r="BY65" s="8">
-        <v>103542</v>
+        <v>103527</v>
       </c>
       <c r="BZ65" s="8">
-        <v>99231</v>
+        <v>99222</v>
       </c>
       <c r="CA65" s="8">
-        <v>98575</v>
+        <v>98589</v>
       </c>
       <c r="CB65" s="8">
-        <v>98708</v>
+        <v>98705</v>
       </c>
       <c r="CC65" s="8">
-        <v>80298</v>
+        <v>80306</v>
       </c>
       <c r="CD65" s="8">
-        <v>73599</v>
+        <v>73604</v>
       </c>
       <c r="CE65" s="8">
-        <v>66852</v>
+        <v>66854</v>
       </c>
       <c r="CF65" s="8">
-        <v>57340</v>
+        <v>57342</v>
       </c>
       <c r="CG65" s="8">
-        <v>54080</v>
+        <v>54086</v>
       </c>
       <c r="CH65" s="8">
-        <v>47029</v>
+        <v>47032</v>
       </c>
       <c r="CI65" s="8">
-        <v>42535</v>
+        <v>42542</v>
       </c>
       <c r="CJ65" s="8">
-        <v>37216</v>
+        <v>37213</v>
       </c>
       <c r="CK65" s="8">
-        <v>32267</v>
+        <v>32271</v>
       </c>
       <c r="CL65" s="8">
-        <v>28041</v>
+        <v>28035</v>
       </c>
       <c r="CM65" s="8">
-        <v>23187</v>
+        <v>23188</v>
       </c>
       <c r="CN65" s="8">
-        <v>18499</v>
+        <v>18500</v>
       </c>
       <c r="CO65" s="8">
-        <v>14960</v>
+        <v>14957</v>
       </c>
       <c r="CP65" s="8">
-        <v>12069</v>
+        <v>12070</v>
       </c>
       <c r="CQ65" s="8">
-        <v>9455</v>
+        <v>9457</v>
       </c>
       <c r="CR65" s="8">
-        <v>7737</v>
+        <v>7736</v>
       </c>
       <c r="CS65" s="8">
-        <v>6028</v>
+        <v>6027</v>
       </c>
       <c r="CT65" s="8">
         <v>4307</v>
@@ -62215,280 +62215,280 @@
         <v>2108</v>
       </c>
       <c r="CY65" s="8">
-        <v>145894</v>
+        <v>145900</v>
       </c>
       <c r="CZ65" s="8">
-        <v>142425</v>
+        <v>142385</v>
       </c>
       <c r="DA65" s="8">
-        <v>144477</v>
+        <v>144446</v>
       </c>
       <c r="DB65" s="8">
-        <v>154853</v>
+        <v>154842</v>
       </c>
       <c r="DC65" s="8">
         <v>150855</v>
       </c>
       <c r="DD65" s="8">
-        <v>150379</v>
+        <v>150389</v>
       </c>
       <c r="DE65" s="8">
-        <v>153441</v>
+        <v>153447</v>
       </c>
       <c r="DF65" s="8">
-        <v>154795</v>
+        <v>154791</v>
       </c>
       <c r="DG65" s="8">
-        <v>158134</v>
+        <v>158144</v>
       </c>
       <c r="DH65" s="8">
-        <v>162657</v>
+        <v>162661</v>
       </c>
       <c r="DI65" s="8">
-        <v>161192</v>
+        <v>161210</v>
       </c>
       <c r="DJ65" s="8">
-        <v>163270</v>
+        <v>163281</v>
       </c>
       <c r="DK65" s="8">
-        <v>164517</v>
+        <v>164505</v>
       </c>
       <c r="DL65" s="8">
-        <v>164977</v>
+        <v>164969</v>
       </c>
       <c r="DM65" s="8">
-        <v>163426</v>
+        <v>163430</v>
       </c>
       <c r="DN65" s="8">
-        <v>165438</v>
+        <v>165449</v>
       </c>
       <c r="DO65" s="8">
-        <v>163736</v>
+        <v>163717</v>
       </c>
       <c r="DP65" s="8">
-        <v>164434</v>
+        <v>164435</v>
       </c>
       <c r="DQ65" s="8">
-        <v>165488</v>
+        <v>165624</v>
       </c>
       <c r="DR65" s="8">
-        <v>168215</v>
+        <v>168173</v>
       </c>
       <c r="DS65" s="8">
-        <v>168591</v>
+        <v>168623</v>
       </c>
       <c r="DT65" s="8">
-        <v>168514</v>
+        <v>168543</v>
       </c>
       <c r="DU65" s="8">
-        <v>170342</v>
+        <v>170258</v>
       </c>
       <c r="DV65" s="8">
-        <v>177107</v>
+        <v>176894</v>
       </c>
       <c r="DW65" s="8">
-        <v>186898</v>
+        <v>186613</v>
       </c>
       <c r="DX65" s="8">
-        <v>193305</v>
+        <v>193151</v>
       </c>
       <c r="DY65" s="8">
-        <v>195414</v>
+        <v>195322</v>
       </c>
       <c r="DZ65" s="8">
-        <v>199739</v>
+        <v>199746</v>
       </c>
       <c r="EA65" s="8">
-        <v>203181</v>
+        <v>203209</v>
       </c>
       <c r="EB65" s="8">
-        <v>204831</v>
+        <v>204919</v>
       </c>
       <c r="EC65" s="8">
-        <v>208161</v>
+        <v>208210</v>
       </c>
       <c r="ED65" s="8">
-        <v>206984</v>
+        <v>206895</v>
       </c>
       <c r="EE65" s="8">
-        <v>206692</v>
+        <v>206630</v>
       </c>
       <c r="EF65" s="8">
-        <v>206501</v>
+        <v>206523</v>
       </c>
       <c r="EG65" s="8">
-        <v>208840</v>
+        <v>208878</v>
       </c>
       <c r="EH65" s="8">
-        <v>208342</v>
+        <v>208327</v>
       </c>
       <c r="EI65" s="8">
-        <v>204374</v>
+        <v>204375</v>
       </c>
       <c r="EJ65" s="8">
-        <v>203033</v>
+        <v>203023</v>
       </c>
       <c r="EK65" s="8">
-        <v>201110</v>
+        <v>201091</v>
       </c>
       <c r="EL65" s="8">
-        <v>200894</v>
+        <v>200913</v>
       </c>
       <c r="EM65" s="8">
-        <v>199463</v>
+        <v>199474</v>
       </c>
       <c r="EN65" s="8">
-        <v>196699</v>
+        <v>196683</v>
       </c>
       <c r="EO65" s="8">
-        <v>194836</v>
+        <v>194816</v>
       </c>
       <c r="EP65" s="8">
-        <v>188421</v>
+        <v>188409</v>
       </c>
       <c r="EQ65" s="8">
-        <v>183322</v>
+        <v>183284</v>
       </c>
       <c r="ER65" s="8">
-        <v>174846</v>
+        <v>174869</v>
       </c>
       <c r="ES65" s="8">
-        <v>170943</v>
+        <v>170962</v>
       </c>
       <c r="ET65" s="8">
-        <v>165746</v>
+        <v>165748</v>
       </c>
       <c r="EU65" s="8">
-        <v>163809</v>
+        <v>163835</v>
       </c>
       <c r="EV65" s="8">
-        <v>162661</v>
+        <v>162658</v>
       </c>
       <c r="EW65" s="8">
-        <v>164099</v>
+        <v>164104</v>
       </c>
       <c r="EX65" s="8">
-        <v>166636</v>
+        <v>166590</v>
       </c>
       <c r="EY65" s="8">
-        <v>170347</v>
+        <v>170304</v>
       </c>
       <c r="EZ65" s="8">
-        <v>176834</v>
+        <v>176786</v>
       </c>
       <c r="FA65" s="8">
-        <v>178552</v>
+        <v>178491</v>
       </c>
       <c r="FB65" s="8">
-        <v>166107</v>
+        <v>166082</v>
       </c>
       <c r="FC65" s="8">
-        <v>163914</v>
+        <v>163895</v>
       </c>
       <c r="FD65" s="8">
-        <v>156797</v>
+        <v>156786</v>
       </c>
       <c r="FE65" s="8">
-        <v>153073</v>
+        <v>153072</v>
       </c>
       <c r="FF65" s="8">
-        <v>152468</v>
+        <v>152452</v>
       </c>
       <c r="FG65" s="8">
-        <v>154327</v>
+        <v>154319</v>
       </c>
       <c r="FH65" s="8">
-        <v>158475</v>
+        <v>158466</v>
       </c>
       <c r="FI65" s="8">
-        <v>160009</v>
+        <v>159998</v>
       </c>
       <c r="FJ65" s="8">
-        <v>158349</v>
+        <v>158329</v>
       </c>
       <c r="FK65" s="8">
-        <v>157082</v>
+        <v>157069</v>
       </c>
       <c r="FL65" s="8">
-        <v>151481</v>
+        <v>151448</v>
       </c>
       <c r="FM65" s="8">
-        <v>148008</v>
+        <v>148029</v>
       </c>
       <c r="FN65" s="8">
-        <v>144997</v>
+        <v>145036</v>
       </c>
       <c r="FO65" s="8">
-        <v>140432</v>
+        <v>140425</v>
       </c>
       <c r="FP65" s="8">
-        <v>136799</v>
+        <v>136771</v>
       </c>
       <c r="FQ65" s="8">
-        <v>132867</v>
+        <v>132870</v>
       </c>
       <c r="FR65" s="8">
         <v>128151</v>
       </c>
       <c r="FS65" s="8">
-        <v>125506</v>
+        <v>125509</v>
       </c>
       <c r="FT65" s="8">
-        <v>120739</v>
+        <v>120746</v>
       </c>
       <c r="FU65" s="8">
-        <v>118390</v>
+        <v>118397</v>
       </c>
       <c r="FV65" s="8">
-        <v>115014</v>
+        <v>115007</v>
       </c>
       <c r="FW65" s="8">
-        <v>110070</v>
+        <v>110064</v>
       </c>
       <c r="FX65" s="8">
-        <v>108158</v>
+        <v>108166</v>
       </c>
       <c r="FY65" s="8">
-        <v>108944</v>
+        <v>108939</v>
       </c>
       <c r="FZ65" s="8">
-        <v>88687</v>
+        <v>88695</v>
       </c>
       <c r="GA65" s="8">
-        <v>82949</v>
+        <v>82966</v>
       </c>
       <c r="GB65" s="8">
-        <v>76190</v>
+        <v>76197</v>
       </c>
       <c r="GC65" s="8">
-        <v>66899</v>
+        <v>66898</v>
       </c>
       <c r="GD65" s="8">
-        <v>62984</v>
+        <v>62990</v>
       </c>
       <c r="GE65" s="8">
-        <v>56760</v>
+        <v>56765</v>
       </c>
       <c r="GF65" s="8">
-        <v>52715</v>
+        <v>52717</v>
       </c>
       <c r="GG65" s="8">
-        <v>48245</v>
+        <v>48240</v>
       </c>
       <c r="GH65" s="8">
-        <v>43262</v>
+        <v>43256</v>
       </c>
       <c r="GI65" s="8">
-        <v>38288</v>
+        <v>38289</v>
       </c>
       <c r="GJ65" s="8">
-        <v>33254</v>
+        <v>33253</v>
       </c>
       <c r="GK65" s="8">
-        <v>28267</v>
+        <v>28265</v>
       </c>
       <c r="GL65" s="8">
-        <v>23436</v>
+        <v>23434</v>
       </c>
       <c r="GM65" s="8">
         <v>20170</v>
@@ -62503,7 +62503,7 @@
         <v>11386</v>
       </c>
       <c r="GQ65" s="8">
-        <v>8477</v>
+        <v>8476</v>
       </c>
       <c r="GR65" s="8">
         <v>6402</v>
@@ -62518,148 +62518,148 @@
         <v>5237</v>
       </c>
       <c r="GV65" s="8">
-        <v>299868</v>
+        <v>299871</v>
       </c>
       <c r="GW65" s="8">
-        <v>292641</v>
+        <v>292565</v>
       </c>
       <c r="GX65" s="8">
-        <v>297299</v>
+        <v>297247</v>
       </c>
       <c r="GY65" s="8">
-        <v>317661</v>
+        <v>317636</v>
       </c>
       <c r="GZ65" s="8">
-        <v>309974</v>
+        <v>309964</v>
       </c>
       <c r="HA65" s="8">
-        <v>308754</v>
+        <v>308758</v>
       </c>
       <c r="HB65" s="8">
-        <v>316300</v>
+        <v>316292</v>
       </c>
       <c r="HC65" s="8">
-        <v>318696</v>
+        <v>318694</v>
       </c>
       <c r="HD65" s="8">
-        <v>325414</v>
+        <v>325421</v>
       </c>
       <c r="HE65" s="8">
-        <v>334684</v>
+        <v>334692</v>
       </c>
       <c r="HF65" s="8">
-        <v>332482</v>
+        <v>332524</v>
       </c>
       <c r="HG65" s="8">
-        <v>335866</v>
+        <v>335877</v>
       </c>
       <c r="HH65" s="8">
-        <v>339173</v>
+        <v>339168</v>
       </c>
       <c r="HI65" s="8">
-        <v>338931</v>
+        <v>338928</v>
       </c>
       <c r="HJ65" s="8">
-        <v>336115</v>
+        <v>336123</v>
       </c>
       <c r="HK65" s="8">
-        <v>339736</v>
+        <v>339754</v>
       </c>
       <c r="HL65" s="8">
-        <v>337187</v>
+        <v>337135</v>
       </c>
       <c r="HM65" s="8">
-        <v>338118</v>
+        <v>338081</v>
       </c>
       <c r="HN65" s="8">
-        <v>342149</v>
+        <v>342301</v>
       </c>
       <c r="HO65" s="8">
-        <v>347170</v>
+        <v>347015</v>
       </c>
       <c r="HP65" s="8">
-        <v>350252</v>
+        <v>350302</v>
       </c>
       <c r="HQ65" s="8">
-        <v>351531</v>
+        <v>351553</v>
       </c>
       <c r="HR65" s="8">
-        <v>355044</v>
+        <v>354924</v>
       </c>
       <c r="HS65" s="8">
-        <v>368697</v>
+        <v>368376</v>
       </c>
       <c r="HT65" s="8">
-        <v>389343</v>
+        <v>388852</v>
       </c>
       <c r="HU65" s="8">
-        <v>398744</v>
+        <v>398476</v>
       </c>
       <c r="HV65" s="8">
-        <v>398981</v>
+        <v>398781</v>
       </c>
       <c r="HW65" s="8">
-        <v>405125</v>
+        <v>405106</v>
       </c>
       <c r="HX65" s="8">
-        <v>410034</v>
+        <v>410059</v>
       </c>
       <c r="HY65" s="8">
-        <v>412703</v>
+        <v>412790</v>
       </c>
       <c r="HZ65" s="8">
-        <v>418199</v>
+        <v>418265</v>
       </c>
       <c r="IA65" s="8">
-        <v>413319</v>
+        <v>413114</v>
       </c>
       <c r="IB65" s="8">
-        <v>410965</v>
+        <v>410811</v>
       </c>
       <c r="IC65" s="8">
-        <v>408824</v>
+        <v>408797</v>
       </c>
       <c r="ID65" s="8">
-        <v>413817</v>
+        <v>413851</v>
       </c>
       <c r="IE65" s="8">
-        <v>413260</v>
+        <v>413217</v>
       </c>
       <c r="IF65" s="8">
-        <v>405683</v>
+        <v>405665</v>
       </c>
       <c r="IG65" s="8">
-        <v>401190</v>
+        <v>401146</v>
       </c>
       <c r="IH65" s="8">
-        <v>399125</v>
+        <v>399089</v>
       </c>
       <c r="II65" s="8">
-        <v>399551</v>
+        <v>399542</v>
       </c>
       <c r="IJ65" s="8">
-        <v>395948</v>
+        <v>395930</v>
       </c>
       <c r="IK65" s="8">
-        <v>390993</v>
+        <v>390949</v>
       </c>
       <c r="IL65" s="8">
-        <v>388101</v>
+        <v>388073</v>
       </c>
       <c r="IM65" s="8">
-        <v>374835</v>
+        <v>374799</v>
       </c>
       <c r="IN65" s="8">
-        <v>363000</v>
+        <v>362948</v>
       </c>
       <c r="IO65" s="8">
-        <v>344728</v>
+        <v>344759</v>
       </c>
       <c r="IP65" s="8">
-        <v>335895</v>
+        <v>335903</v>
       </c>
       <c r="IQ65" s="8">
-        <v>325571</v>
+        <v>325572</v>
       </c>
     </row>
   </sheetData>
@@ -73174,151 +73174,151 @@
         <v>45809</v>
       </c>
       <c r="B65" s="8">
-        <v>322410</v>
+        <v>322448</v>
       </c>
       <c r="C65" s="8">
-        <v>322462</v>
+        <v>322452</v>
       </c>
       <c r="D65" s="8">
-        <v>324729</v>
+        <v>324735</v>
       </c>
       <c r="E65" s="8">
-        <v>329198</v>
+        <v>329136</v>
       </c>
       <c r="F65" s="8">
-        <v>335994</v>
+        <v>335946</v>
       </c>
       <c r="G65" s="8">
-        <v>347266</v>
+        <v>347234</v>
       </c>
       <c r="H65" s="8">
-        <v>349710</v>
+        <v>349627</v>
       </c>
       <c r="I65" s="8">
-        <v>326201</v>
+        <v>326177</v>
       </c>
       <c r="J65" s="8">
-        <v>321085</v>
+        <v>321054</v>
       </c>
       <c r="K65" s="8">
-        <v>307473</v>
+        <v>307448</v>
       </c>
       <c r="L65" s="8">
         <v>300328</v>
       </c>
       <c r="M65" s="8">
-        <v>298963</v>
+        <v>298922</v>
       </c>
       <c r="N65" s="8">
-        <v>301761</v>
+        <v>301735</v>
       </c>
       <c r="O65" s="8">
-        <v>309521</v>
+        <v>309497</v>
       </c>
       <c r="P65" s="8">
-        <v>312180</v>
+        <v>312155</v>
       </c>
       <c r="Q65" s="8">
-        <v>308617</v>
+        <v>308556</v>
       </c>
       <c r="R65" s="8">
-        <v>304563</v>
+        <v>304494</v>
       </c>
       <c r="S65" s="8">
-        <v>292367</v>
+        <v>292258</v>
       </c>
       <c r="T65" s="8">
-        <v>285544</v>
+        <v>285550</v>
       </c>
       <c r="U65" s="8">
-        <v>278163</v>
+        <v>278198</v>
       </c>
       <c r="V65" s="8">
-        <v>269323</v>
+        <v>269296</v>
       </c>
       <c r="W65" s="8">
-        <v>262716</v>
+        <v>262663</v>
       </c>
       <c r="X65" s="8">
-        <v>253173</v>
+        <v>253161</v>
       </c>
       <c r="Y65" s="8">
-        <v>243949</v>
+        <v>243933</v>
       </c>
       <c r="Z65" s="8">
-        <v>239482</v>
+        <v>239475</v>
       </c>
       <c r="AA65" s="8">
-        <v>230400</v>
+        <v>230387</v>
       </c>
       <c r="AB65" s="8">
-        <v>225718</v>
+        <v>225751</v>
       </c>
       <c r="AC65" s="8">
-        <v>218556</v>
+        <v>218534</v>
       </c>
       <c r="AD65" s="8">
-        <v>209301</v>
+        <v>209286</v>
       </c>
       <c r="AE65" s="8">
-        <v>206733</v>
+        <v>206755</v>
       </c>
       <c r="AF65" s="8">
-        <v>207652</v>
+        <v>207644</v>
       </c>
       <c r="AG65" s="8">
-        <v>168985</v>
+        <v>169001</v>
       </c>
       <c r="AH65" s="8">
-        <v>156548</v>
+        <v>156570</v>
       </c>
       <c r="AI65" s="8">
-        <v>143042</v>
+        <v>143051</v>
       </c>
       <c r="AJ65" s="8">
-        <v>124239</v>
+        <v>124240</v>
       </c>
       <c r="AK65" s="8">
-        <v>117064</v>
+        <v>117076</v>
       </c>
       <c r="AL65" s="8">
-        <v>103789</v>
+        <v>103797</v>
       </c>
       <c r="AM65" s="8">
-        <v>95250</v>
+        <v>95259</v>
       </c>
       <c r="AN65" s="8">
-        <v>85461</v>
+        <v>85453</v>
       </c>
       <c r="AO65" s="8">
-        <v>75529</v>
+        <v>75527</v>
       </c>
       <c r="AP65" s="8">
-        <v>66329</v>
+        <v>66324</v>
       </c>
       <c r="AQ65" s="8">
         <v>56441</v>
       </c>
       <c r="AR65" s="8">
-        <v>46766</v>
+        <v>46765</v>
       </c>
       <c r="AS65" s="8">
-        <v>38396</v>
+        <v>38391</v>
       </c>
       <c r="AT65" s="8">
-        <v>32239</v>
+        <v>32240</v>
       </c>
       <c r="AU65" s="8">
-        <v>26151</v>
+        <v>26153</v>
       </c>
       <c r="AV65" s="8">
-        <v>21925</v>
+        <v>21924</v>
       </c>
       <c r="AW65" s="8">
-        <v>17414</v>
+        <v>17413</v>
       </c>
       <c r="AX65" s="8">
-        <v>12784</v>
+        <v>12783</v>
       </c>
       <c r="AY65" s="8">
         <v>9193</v>
